--- a/inspection_forms/019_lead_acid_battery_safety_assessment--inspection_forms.xlsx
+++ b/inspection_forms/019_lead_acid_battery_safety_assessment--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment</t>
+          <t>battery_storage</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>battery_storage</t>
+          <t>Battery Storage</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_form</t>
+          <t>handling_practices</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>handling_practices</t>
+          <t>Handling Practices</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_template</t>
+          <t>training_readiness</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>training_readiness</t>
+          <t>Training Readiness</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_templates</t>
+          <t>centralized_data_collection</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>centralized_data_collection</t>
+          <t>Centralized Data Collection</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_templates_by_jotform</t>
+          <t>reliable_form_submission</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>reliable_form_submission</t>
+          <t>Reliable Form Submission</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_template_by_jotform</t>
+          <t>battery_storage_and_handling_inspection</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>battery_storage_and_handling_inspection</t>
+          <t>Battery Storage and Handling Inspection</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_templates</t>
+          <t>lead_acid_batteries</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>lead_acid_batteries</t>
+          <t>Lead Acid Batteries</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform</t>
+          <t>storage_facility</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>storage_facility</t>
+          <t>Storage Facility</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_template_by_jotform</t>
+          <t>inspection_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>inspection_date</t>
+          <t>Inspection Date</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform</t>
+          <t>inspection_time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>inspection_time</t>
+          <t>Inspection Time</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_templates_by_jotform</t>
+          <t>inspection_frequency</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>inspection_frequency</t>
+          <t>Inspection Frequency</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform</t>
+          <t>inspection_by</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>inspection_by</t>
+          <t>Inspection By</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_template_by_jotform</t>
+          <t>inspection_type</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>inspection_type</t>
+          <t>Inspection Type</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,18 +819,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_form_by_jotform</t>
+          <t>lead_acid_battery_handling</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>lead_battery_storage</t>
+          <t>Lead Acid Battery Handling</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,35 +842,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform</t>
+          <t>lead_acid_batteries_storage</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>lead_battery_handling</t>
+          <t>Lead Acid Batteries Storage and Handling</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_form_by_jotform</t>
+          <t>signature</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>training_status</t>
+          <t>Signature</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>signature</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,17 +952,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_form_by_jotform</t>
+          <t>lead_acid_batteries_storage_and_handling</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Lead Acid Batteries Storage and Handling (2)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,17 +975,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform</t>
+          <t>lead_acid_batteries_handling</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Lead Acid Batteries Handling</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -998,17 +998,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform</t>
+          <t>lead_acid_batteries_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>Lead Acid Batteries 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1021,161 +1021,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform</t>
+          <t>inspection_date_and_time</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>by</t>
+          <t>Inspection Date and Time</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>inspection_type</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>lead_acid_battery_safety_form_by_jotform</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>lead_acid_batteries</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>lead_acid_battery_handling</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>lead_acid_battery_safety_form_by_jotform</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>lead_acid_batteries_storage</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>lead_acid_batteries_handling</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>lead_acid_batteries_storage</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1052,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1218,612 +1080,442 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_choices</t>
+          <t>battery_storage_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'option_1'}</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_choices</t>
+          <t>battery_storage_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'option_2'}</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_form_choices</t>
+          <t>handling_practices_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'option_3'}</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_form_choices</t>
+          <t>handling_practices_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'option_4'}</t>
+          <t>option 4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_form_choices</t>
+          <t>handling_practices_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'option_5'}</t>
+          <t>option 5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_templates_by_jotform_choices</t>
+          <t>reliable_form_submission_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_6'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'option_6'}</t>
+          <t>option 6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_templates_by_jotform_choices</t>
+          <t>reliable_form_submission_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_7'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'option_7'}</t>
+          <t>option 7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_templates_choices</t>
+          <t>lead_acid_batteries_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_8'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'option_8'}</t>
+          <t>option 8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_templates_choices</t>
+          <t>lead_acid_batteries_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_9'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'option_9'}</t>
+          <t>option 9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_templates_choices</t>
+          <t>lead_acid_batteries_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_10'}</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'option_10'}</t>
+          <t>option 10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform_choices</t>
+          <t>storage_facility_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_11'}</t>
+          <t>option_11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'option_11'}</t>
+          <t>option 11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform_choices</t>
+          <t>storage_facility_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_12'}</t>
+          <t>option_12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'option_12'}</t>
+          <t>option 12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_templates_by_jotform_choices</t>
+          <t>inspection_frequency_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_13'}</t>
+          <t>option_13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'option_13'}</t>
+          <t>option 13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_templates_by_jotform_choices</t>
+          <t>inspection_frequency_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_14'}</t>
+          <t>option_14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'option_14'}</t>
+          <t>option 14</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_templates_by_jotform_choices</t>
+          <t>inspection_by_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_15'}</t>
+          <t>option_16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'option_15'}</t>
+          <t>option 16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform_choices</t>
+          <t>inspection_by_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_16'}</t>
+          <t>option_17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'option_16'}</t>
+          <t>option 17</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform_choices</t>
+          <t>inspection_type_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_17'}</t>
+          <t>option_18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'option_17'}</t>
+          <t>option 18</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_template_by_jotform_choices</t>
+          <t>inspection_type_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_18'}</t>
+          <t>option_19</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'option_18'}</t>
+          <t>option 19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_template_by_jotform_choices</t>
+          <t>inspection_type_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_19'}</t>
+          <t>option_20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'option_19'}</t>
+          <t>option 20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_template_by_jotform_choices</t>
+          <t>signature_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_20'}</t>
+          <t>option_25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'option_20'}</t>
+          <t>option 25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform_choices</t>
+          <t>signature_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_21'}</t>
+          <t>option_26</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'option_21'}</t>
+          <t>option 26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform_choices</t>
+          <t>lead_acid_batteries_storage_and_handling_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_22'}</t>
+          <t>option_33</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'option_22'}</t>
+          <t>option 33</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_form_by_jotform_choices</t>
+          <t>lead_acid_batteries_storage_and_handling_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_23'}</t>
+          <t>option_34</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'option_23'}</t>
+          <t>option 34</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_form_by_jotform_choices</t>
+          <t>lead_acid_batteries_storage_and_handling_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_24'}</t>
+          <t>option_35</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'option_24'}</t>
+          <t>option 35</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform_choices</t>
+          <t>lead_acid_batteries_handling_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_25'}</t>
+          <t>option_36</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'option_25'}</t>
+          <t>option 36</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform_choices</t>
+          <t>lead_acid_batteries_handling_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_26'}</t>
+          <t>option_37</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'option_26'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'option_27'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'option_27'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'option_28'}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'option_28'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'option_29'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'option_29'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'option_30'}</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'option_30'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'option_31'}</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'option_31'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'option_32'}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'option_32'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>lead_acid_battery_safety_form_by_jotform_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'option_33'}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'option_33'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>lead_acid_battery_safety_form_by_jotform_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'option_34'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'option_34'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'option_35'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'option_35'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>lead_acid_battery_safety_assessment_form_by_jotform_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'option_36'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'option_36'}</t>
+          <t>option 37</t>
         </is>
       </c>
     </row>
